--- a/Employee_Reports_wi48/Nino Vercide Arda Q0499.xlsx
+++ b/Employee_Reports_wi48/Nino Vercide Arda Q0499.xlsx
@@ -578,11 +578,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -627,11 +627,11 @@
         </is>
       </c>
       <c r="H4" s="3" t="n">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -676,11 +676,11 @@
         </is>
       </c>
       <c r="H5" s="4" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J5" s="4" t="inlineStr">
@@ -725,11 +725,11 @@
         </is>
       </c>
       <c r="H6" s="3" t="n">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -774,11 +774,11 @@
         </is>
       </c>
       <c r="H7" s="3" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -823,11 +823,11 @@
         </is>
       </c>
       <c r="H8" s="3" t="n">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -872,11 +872,11 @@
         </is>
       </c>
       <c r="H9" s="3" t="n">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -921,11 +921,11 @@
         </is>
       </c>
       <c r="H10" s="4" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J10" s="4" t="inlineStr">
@@ -970,11 +970,11 @@
         </is>
       </c>
       <c r="H11" s="3" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -1019,11 +1019,11 @@
         </is>
       </c>
       <c r="H12" s="3" t="n">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
@@ -1068,11 +1068,11 @@
         </is>
       </c>
       <c r="H13" s="3" t="n">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -1117,11 +1117,11 @@
         </is>
       </c>
       <c r="H14" s="4" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J14" s="4" t="inlineStr">
@@ -1166,11 +1166,11 @@
         </is>
       </c>
       <c r="H15" s="3" t="n">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
@@ -1215,11 +1215,11 @@
         </is>
       </c>
       <c r="H16" s="3" t="n">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
@@ -1264,11 +1264,11 @@
         </is>
       </c>
       <c r="H17" s="3" t="n">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
@@ -1313,11 +1313,11 @@
         </is>
       </c>
       <c r="H18" s="4" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J18" s="4" t="inlineStr">
@@ -1362,11 +1362,11 @@
         </is>
       </c>
       <c r="H19" s="3" t="n">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
@@ -1411,11 +1411,11 @@
         </is>
       </c>
       <c r="H20" s="3" t="n">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
@@ -1460,11 +1460,11 @@
         </is>
       </c>
       <c r="H21" s="3" t="n">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
@@ -1509,11 +1509,11 @@
         </is>
       </c>
       <c r="H22" s="3" t="n">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
@@ -1558,11 +1558,11 @@
         </is>
       </c>
       <c r="H23" s="3" t="n">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
@@ -1607,11 +1607,11 @@
         </is>
       </c>
       <c r="H24" s="3" t="n">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
@@ -1656,11 +1656,11 @@
         </is>
       </c>
       <c r="H25" s="3" t="n">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
@@ -1705,11 +1705,11 @@
         </is>
       </c>
       <c r="H26" s="3" t="n">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
@@ -1742,11 +1742,11 @@
         </is>
       </c>
       <c r="H27" s="3" t="n">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
@@ -1791,11 +1791,11 @@
         </is>
       </c>
       <c r="H28" s="3" t="n">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
@@ -1840,11 +1840,11 @@
         </is>
       </c>
       <c r="H29" s="3" t="n">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J29" s="3" t="inlineStr">
@@ -1863,9 +1863,21 @@
           <t>Procedure For Handling New or Unfamilliar Task (SOPs)</t>
         </is>
       </c>
-      <c r="C30" s="5" t="inlineStr"/>
-      <c r="D30" s="5" t="inlineStr"/>
-      <c r="E30" s="5" t="inlineStr"/>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>IMS</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>LSME-IMS-SOP-022</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>SOP</t>
+        </is>
+      </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
           <t>25-Mar-2025</t>
@@ -1877,11 +1889,11 @@
         </is>
       </c>
       <c r="H30" s="5" t="n">
-        <v>-110</v>
+        <v>-113</v>
       </c>
       <c r="I30" s="5" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J30" s="5" t="inlineStr">
@@ -1900,9 +1912,21 @@
           <t>Equipment Operation Procedure(QDF-SOP-003) (SOPs)</t>
         </is>
       </c>
-      <c r="C31" s="3" t="inlineStr"/>
-      <c r="D31" s="3" t="inlineStr"/>
-      <c r="E31" s="3" t="inlineStr"/>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>DFWH</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>LSME-QDF-SOP-003</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>SOP</t>
+        </is>
+      </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
           <t>07-May-2026</t>
@@ -1914,11 +1938,11 @@
         </is>
       </c>
       <c r="H31" s="3" t="n">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J31" s="3" t="inlineStr">
@@ -1963,11 +1987,11 @@
         </is>
       </c>
       <c r="H32" s="3" t="n">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
@@ -2000,11 +2024,11 @@
         </is>
       </c>
       <c r="H33" s="3" t="n">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J33" s="3" t="inlineStr">
